--- a/artfynd/S 1092-2023 artfynd.xlsx
+++ b/artfynd/S 1092-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136309467</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1092-2023 artfynd.xlsx
+++ b/artfynd/S 1092-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136309467</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1092-2023 artfynd.xlsx
+++ b/artfynd/S 1092-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136309467</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136309466</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136309465</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1092-2023 artfynd.xlsx
+++ b/artfynd/S 1092-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136309467</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
